--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESCOVA ARRANQUE - 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESCOVA ARRANQUE - 02_02.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EA UNIK YBR125/ XTZ125/ FACTOR125</t>
+          <t>ESCOVA ARRANQUE  UNIK YBR125/ XTZ125/ FACTOR125</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EA MAGNETRON YBR125 2000 A 2007/ FACTOR125 2002 A 2015 90256010</t>
+          <t>ESCOVA ARRANQUE  MAGNETRON YBR125 2000 A 2007/ FACTOR125 2002 A 2015 90256010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EA TMAC BIZ125 2011/ CG TITAN150 2004 A 2015/ FAN160/ NXR125-150-160</t>
+          <t>ESCOVA ARRANQUE  TMAC BIZ125 2011/ CG TITAN150 2004 A 2015/ FAN160/ NXR125-150-160</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EA MAGNETRON YS250 FAZER 2012 90203212</t>
+          <t>ESCOVA ARRANQUE  MAGNETRON YS250 FAZER 2012 90203212</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EA IRON YS150 FAZER 045410</t>
+          <t>ESCOVA ARRANQUE  IRON YS150 FAZER 045410</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EA IRON CB300/ XRE300/ CRF250F 2008 EM DIANTE 017136</t>
+          <t>ESCOVA ARRANQUE  IRON CB300/ XRE300/ CRF250F 2008 EM DIANTE 017136</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EA IRON YS250 FAZER/ XTZ250 2013 EM DIANTE 176831</t>
+          <t>ESCOVA ARRANQUE  IRON YS250 FAZER/ XTZ250 2013 EM DIANTE 176831</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EA IRON BIZES 045416</t>
+          <t>ESCOVA ARRANQUE  IRON BIZES 045416</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EA ZOUIL TITAN CG125 KS 2000 A 2004/ CBX250 2001 A 2008/ XTZ250 2007 A 2012/ NXR125-150 2003 A 2005</t>
+          <t>ESCOVA ARRANQUE  ZOUIL TITAN CG125 KS 2000 A 2004/ CBX250 2001 A 2008/ XTZ250 2007 A 2012/ NXR125-150 2003 A 2005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EA IRON YES125/ INTRUDER125/ BURGMAN 045415</t>
+          <t>ESCOVA ARRANQUE  IRON YES125/ INTRUDER125/ BURGMAN 045415</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EA MAGNETRON CG TITAN150/ FAN125 2009 A 2013/ NXR125 2013 EM DIANTE 90205020</t>
+          <t>ESCOVA ARRANQUE  MAGNETRON CG TITAN150/ FAN125 2009 A 2013/ NXR125 2013 EM DIANTE 90205020</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">EA SCT FAZER150 </t>
+          <t xml:space="preserve">ESCOVA ARRANQUE  SCT FAZER150 </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EA CONDOR CBX/ NX/ TITAN 2000 1101117</t>
+          <t>ESCOVA ARRANQUE  CONDOR CBX/ NX/ TITAN 2000 1101117</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EA MAGNETRON FAN 2009/ CG TITAN150 90205050</t>
+          <t>ESCOVA ARRANQUE  MAGNETRON FAN 2009/ CG TITAN150 90205050</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -759,7 +759,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EA MAGENTRON 4 POLOS CG125 2000 EM DIANTE 90206080</t>
+          <t>ESCOVA ARRANQUE  MAGENTRON 4 POLOS CG125 2000 EM DIANTE 90206080</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,7 +776,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">EA CONDOR YES125 </t>
+          <t xml:space="preserve">ESCOVA ARRANQUE  CONDOR YES125 </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESCOVA ARRANQUE - 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESCOVA ARRANQUE - 02_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +552,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,11 +572,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -600,7 +584,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ESCOVA ARRANQUE  IRON BIZES 045416</t>
+          <t>ESCOVA ARRANQUE  IRON BIZ 045416</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -608,7 +592,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,11 +612,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -654,11 +632,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -679,11 +652,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -704,11 +672,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -729,11 +692,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -750,7 +708,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -767,7 +724,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -782,11 +738,6 @@
       <c r="D17" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
     </row>
